--- a/relatorio_estoque_peps_cmv.xlsx
+++ b/relatorio_estoque_peps_cmv.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Movimentações" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Lotes" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="CMV Mês Atual" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Despesas" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,13 +22,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +50,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,17 +434,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sistema</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
@@ -440,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Estoque Restaurante PEPS + CMV + Perdas</t>
+          <t>Estoque Restaurante PEPS + CMV + Perdas + OCR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -465,51 +478,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Produto</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Unidade</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Estoque Mínimo</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Qtd Atual</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Valor Estoque</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Custo Médio Atual</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Alerta</t>
         </is>
@@ -538,10 +551,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G2" t="n">
-        <v>145</v>
+        <v>139.2</v>
       </c>
       <c r="H2" t="n">
         <v>2.9</v>
@@ -575,10 +588,10 @@
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>275</v>
+        <v>247.5</v>
       </c>
       <c r="H3" t="n">
         <v>5.5</v>
@@ -591,34 +604,34 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>2293</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>CROISSANT DE FRANGO COM REQUEIJAO SC 2,8 KG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Mercadoria</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>145</v>
+        <v>222</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9</v>
+        <v>74</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -628,34 +641,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1068</v>
+        <v>2294</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Croissant Frango Requeijão</t>
+          <t>CROISSANT DE PIZZA LIGHT SC C 2,5 KG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Mercadoria</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>UN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>45.8</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>132.82</v>
+        <v>74</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9</v>
+        <v>74</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -665,34 +678,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>2295</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CROISSANT INT DE MINAS COM CEB SC 2,5 KG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mercadoria</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>1</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Croissant Queijo Presunto</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Croissant</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" t="n">
-        <v>50</v>
-      </c>
       <c r="G6" t="n">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9</v>
+        <v>80</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -702,34 +715,34 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>2292</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CROISSANT MISTO SC 2,8 KG</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mercadoria</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Croissant Ricota</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Croissant</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" t="n">
-        <v>50</v>
-      </c>
       <c r="G7" t="n">
-        <v>145</v>
+        <v>222</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9</v>
+        <v>74</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -739,16 +752,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>F100E - BATERIA 100AMP</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mercadoria</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -757,35 +770,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>136.3</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2.899999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>⚠️ Baixo</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>1068</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pastel Carne</t>
+          <t>Croissant Frango Requeijão</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -794,16 +807,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>32.8</v>
       </c>
       <c r="G9" t="n">
-        <v>95</v>
+        <v>95.11999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -813,16 +826,16 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pastel Natural Frango</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -831,16 +844,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>46.8</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>88.91999999999999</v>
+        <v>145</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -850,16 +863,16 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pastel Queijo</t>
+          <t>Croissant Ricota</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -868,16 +881,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
         <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -887,11 +900,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TC1014 - TAMPA TANQUE ROSCA INT VW MODERNO</t>
+          <t>F100E - BATERIA 100AMP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -924,36 +937,184 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pastel Carne</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Pastel</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G13" t="n">
+        <v>95</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pastel Natural Frango</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pastel</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G14" t="n">
+        <v>88.91999999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pastel Queijo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pastel</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" t="n">
+        <v>50</v>
+      </c>
+      <c r="G15" t="n">
+        <v>95</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>43</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TC1014 - TAMPA TANQUE ROSCA INT VW MODERNO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Mercadoria</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>⚠️ Baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>8</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Torta Frango</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Torta</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E17" t="n">
         <v>10</v>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>⚠️ Baixo</t>
         </is>
@@ -970,86 +1131,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Produto</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo Saída</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Motivo Saída</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Quantidade</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Valor Unitário</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Valor Total</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Receita Venda</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>CMV PEPS</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Custo Médio Após Saída</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Tipo Saída</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Motivo Saída</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Fornecedor</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Chave NF-e</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
@@ -1057,7 +1218,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1066,12 +1227,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pastel Natural Frango</t>
+          <t>Croissant Frango Requeijão</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1079,41 +1240,41 @@
           <t>Saída</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" t="n">
         <v>12.9</v>
       </c>
-      <c r="H2" t="n">
-        <v>20.64</v>
-      </c>
-      <c r="I2" t="n">
-        <v>20.64</v>
-      </c>
       <c r="J2" t="n">
-        <v>3.04</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Venda</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+        <v>77.40000000000001</v>
+      </c>
+      <c r="L2" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.9</v>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Saída automática por foto de cupom. Detectado: sa PROMOCAO GUARANA NATURAL</t>
+          <t>Saída automática por foto de cupom. Detectado: ,e6 CROLSSANT INT. FRANGO REQUEIJAO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1135,41 +1296,41 @@
           <t>Saída</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="n">
         <v>12.9</v>
       </c>
-      <c r="H3" t="n">
-        <v>20.64</v>
-      </c>
-      <c r="I3" t="n">
-        <v>20.64</v>
-      </c>
       <c r="J3" t="n">
-        <v>4.64</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K3" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="L3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="M3" t="n">
         <v>2.9</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Venda</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Saída automática por foto de cupom. Detectado: 97 PROMO CROIS FRANGO REQUEIJAO</t>
+          <t>Saída automática por foto de cupom. Detectado: ,e6 CROLSSANT INT. FRANGO REQUEIJAO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1178,12 +1339,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pastel Natural Frango</t>
+          <t>Açaí</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Açaí</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1191,41 +1352,37 @@
           <t>Saída</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3.9</v>
-      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>6.24</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>6.24</v>
+        <v>16.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.04</v>
+        <v>84.5</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Venda</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+        <v>84.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5.5</v>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Saída automática por foto de cupom. Detectado: sa PROMOCAO GUARANA NATURAL</t>
-        </is>
-      </c>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1234,12 +1391,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Croissant Frango Requeijão</t>
+          <t>1932231 - EMBREAGEM VISCOSA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Mercadoria</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1247,41 +1404,37 @@
           <t>Saída</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3.9</v>
-      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>6.24</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>6.24</v>
+        <v>16.9</v>
       </c>
       <c r="J5" t="n">
-        <v>4.64</v>
+        <v>33.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2.899999999999999</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Venda</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>33.8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.800000000000004</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.9</v>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Saída automática por foto de cupom. Detectado: 97 PROMO CROIS FRANGO REQUEIJAO</t>
-        </is>
-      </c>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1290,46 +1443,50 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Açaí</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Açaí</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5.5</v>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>275</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>38.7</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+        <v>38.7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.899999999999999</v>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1338,46 +1495,54 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pastel Natural Frango</t>
+          <t>Croissant Frango Requeijão</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>50</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.9</v>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+        <v>12.9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.9</v>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Saída automática por foto de cupom. Detectado: ,e6 CROLSSANT INT. FRANGO REQUEIJAO</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1386,7 +1551,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pastel Queijo</t>
+          <t>Pastel Natural Frango</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1396,36 +1561,44 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G8" t="n">
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="M8" t="n">
         <v>1.9</v>
       </c>
-      <c r="H8" t="n">
-        <v>95</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Saída automática por foto de cupom. Detectado: sa PROMOCAO GUARANA NATURAL</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1434,46 +1607,54 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pastel Carne</t>
+          <t>Croissant Frango Requeijão</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>50</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.9</v>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>95</v>
+        <v>1.6</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>20.64</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+        <v>20.64</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.9</v>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Saída automática por foto de cupom. Detectado: 97 PROMO CROIS FRANGO REQUEIJAO</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1482,46 +1663,54 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croissant Ricota</t>
+          <t>Pastel Natural Frango</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2.9</v>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>145</v>
+        <v>1.6</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+        <v>6.24</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.9</v>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Saída automática por foto de cupom. Detectado: sa PROMOCAO GUARANA NATURAL</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1530,7 +1719,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>Croissant Frango Requeijão</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1540,36 +1729,44 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>50</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2.9</v>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>145</v>
+        <v>1.6</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+        <v>6.24</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.899999999999999</v>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Saída automática por foto de cupom. Detectado: 97 PROMO CROIS FRANGO REQUEIJAO</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1578,12 +1775,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>Açaí</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Açaí</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1591,33 +1788,33 @@
           <t>Entrada</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
         <v>50</v>
       </c>
-      <c r="G12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H12" t="n">
-        <v>145</v>
-      </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1626,54 +1823,46 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croissant Frango Requeijão</t>
+          <t>Pastel Natural Frango</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>12.9</v>
-      </c>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>12.9</v>
+        <v>50</v>
       </c>
       <c r="I13" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9</v>
+        <v>95</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Venda</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Saída automática por foto de cupom. Detectado: ,e6 CROLSSANT INT. FRANGO REQUEIJAO</t>
-        </is>
-      </c>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1682,12 +1871,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croissant Frango Requeijão</t>
+          <t>Pastel Queijo</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1695,37 +1884,33 @@
           <t>Entrada</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
         <v>50</v>
       </c>
-      <c r="G14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H14" t="n">
-        <v>145</v>
-      </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1734,12 +1919,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1932231 - EMBREAGEM VISCOSA</t>
+          <t>Pastel Carne</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mercadoria</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1747,147 +1932,143 @@
           <t>Entrada</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
         <v>50</v>
       </c>
-      <c r="G15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H15" t="n">
-        <v>145</v>
-      </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pastel Queijo</t>
+          <t>Croissant Ricota</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>150</v>
-      </c>
-      <c r="G16" t="n">
-        <v>7.9</v>
-      </c>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>1185</v>
+        <v>50</v>
       </c>
       <c r="I16" t="n">
-        <v>1185</v>
+        <v>2.9</v>
       </c>
       <c r="J16" t="n">
-        <v>255</v>
+        <v>145</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pastel Carne</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>150</v>
-      </c>
-      <c r="G17" t="n">
-        <v>7.9</v>
-      </c>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>1185</v>
+        <v>50</v>
       </c>
       <c r="I17" t="n">
-        <v>1185</v>
+        <v>2.9</v>
       </c>
       <c r="J17" t="n">
-        <v>255</v>
+        <v>145</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pastel Carne</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1895,90 +2076,98 @@
           <t>Entrada</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>150</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.7</v>
-      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>255</v>
+        <v>50</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pastel Queijo</t>
+          <t>Croissant Frango Requeijão</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>150</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1.7</v>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>255</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+        <v>12.9</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.9</v>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Saída automática por foto de cupom. Detectado: ,e6 CROLSSANT INT. FRANGO REQUEIJAO</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croissant Ricota</t>
+          <t>Croissant Frango Requeijão</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1988,84 +2177,92 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
         <v>50</v>
       </c>
-      <c r="G20" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="H20" t="n">
-        <v>445</v>
-      </c>
       <c r="I20" t="n">
-        <v>445</v>
+        <v>2.9</v>
       </c>
       <c r="J20" t="n">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>1932231 - EMBREAGEM VISCOSA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Mercadoria</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>150</v>
-      </c>
-      <c r="G21" t="n">
-        <v>9.199999999999999</v>
-      </c>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>1380</v>
+        <v>50</v>
       </c>
       <c r="I21" t="n">
-        <v>1380</v>
+        <v>2.9</v>
       </c>
       <c r="J21" t="n">
-        <v>285</v>
+        <v>145</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2074,12 +2271,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>Pastel Queijo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2087,33 +2284,33 @@
           <t>Saída</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
         <v>150</v>
       </c>
-      <c r="G22" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1335</v>
-      </c>
       <c r="I22" t="n">
-        <v>1335</v>
+        <v>7.9</v>
       </c>
       <c r="J22" t="n">
-        <v>285</v>
+        <v>1185</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+        <v>1185</v>
+      </c>
+      <c r="L22" t="n">
+        <v>255</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2122,50 +2319,46 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>Pastel Carne</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
         <v>150</v>
       </c>
-      <c r="G23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H23" t="n">
-        <v>285</v>
-      </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1185</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
+        <v>1185</v>
+      </c>
+      <c r="L23" t="n">
+        <v>255</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2174,12 +2367,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>Pastel Carne</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2187,37 +2380,33 @@
           <t>Entrada</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
         <v>150</v>
       </c>
-      <c r="G24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H24" t="n">
-        <v>285</v>
-      </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2226,46 +2415,46 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croissant Ricota</t>
+          <t>Pastel Queijo</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>100</v>
-      </c>
-      <c r="G25" t="n">
-        <v>8.9</v>
-      </c>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>890</v>
+        <v>150</v>
       </c>
       <c r="I25" t="n">
-        <v>890</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>190</v>
+        <v>255</v>
       </c>
       <c r="K25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2284,40 +2473,36 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>150</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1.9</v>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>285</v>
+        <v>50</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="L26" t="n">
+        <v>95</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2326,7 +2511,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2339,33 +2524,33 @@
           <t>Saída</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>25</v>
-      </c>
-      <c r="G27" t="n">
-        <v>7.9</v>
-      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>197.5</v>
+        <v>150</v>
       </c>
       <c r="I27" t="n">
-        <v>197.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>97.5</v>
+        <v>1380</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+        <v>1380</v>
+      </c>
+      <c r="L27" t="n">
+        <v>285</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2374,7 +2559,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2387,33 +2572,33 @@
           <t>Saída</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>45</v>
-      </c>
-      <c r="G28" t="n">
-        <v>7.9</v>
-      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>355.5</v>
+        <v>150</v>
       </c>
       <c r="I28" t="n">
-        <v>355.5</v>
+        <v>8.9</v>
       </c>
       <c r="J28" t="n">
-        <v>130.5</v>
+        <v>1335</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+        <v>1335</v>
+      </c>
+      <c r="L28" t="n">
+        <v>285</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2422,7 +2607,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2432,36 +2617,40 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>10</v>
-      </c>
-      <c r="G29" t="n">
-        <v>7.9</v>
-      </c>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="I29" t="n">
-        <v>79</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
-        <v>39</v>
+        <v>285</v>
       </c>
       <c r="K29" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2470,7 +2659,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2480,36 +2669,40 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>10</v>
-      </c>
-      <c r="G30" t="n">
-        <v>7.9</v>
-      </c>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="I30" t="n">
-        <v>79</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
-        <v>29</v>
+        <v>285</v>
       </c>
       <c r="K30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2518,7 +2711,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>Croissant Ricota</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2531,33 +2724,33 @@
           <t>Saída</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>10</v>
-      </c>
-      <c r="G31" t="n">
-        <v>7.9</v>
-      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>79</v>
+        <v>8.9</v>
       </c>
       <c r="J31" t="n">
-        <v>39</v>
+        <v>890</v>
       </c>
       <c r="K31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+        <v>890</v>
+      </c>
+      <c r="L31" t="n">
+        <v>190</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.9</v>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2566,7 +2759,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>Croissant Ricota</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2576,36 +2769,40 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>45</v>
-      </c>
-      <c r="G32" t="n">
-        <v>6.9</v>
-      </c>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>310.5</v>
+        <v>150</v>
       </c>
       <c r="I32" t="n">
-        <v>310.5</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
-        <v>130.5</v>
+        <v>285</v>
       </c>
       <c r="K32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2614,7 +2811,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2624,36 +2821,36 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>100</v>
-      </c>
-      <c r="G33" t="n">
-        <v>2.9</v>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>290</v>
+        <v>25</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>197.5</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+        <v>197.5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2662,7 +2859,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2675,81 +2872,81 @@
           <t>Saída</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>55</v>
-      </c>
-      <c r="G34" t="n">
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>45</v>
+      </c>
+      <c r="I34" t="n">
         <v>7.9</v>
       </c>
-      <c r="H34" t="n">
-        <v>434.5</v>
-      </c>
-      <c r="I34" t="n">
-        <v>434.5</v>
-      </c>
       <c r="J34" t="n">
-        <v>214.5</v>
+        <v>355.5</v>
       </c>
       <c r="K34" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+        <v>355.5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
+        <v>16</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Croissant Carne</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Croissant</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="n">
         <v>10</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Croissant Carne</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Croissant</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>100</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="I35" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J35" t="n">
+        <v>79</v>
+      </c>
+      <c r="K35" t="n">
+        <v>79</v>
+      </c>
+      <c r="L35" t="n">
+        <v>39</v>
+      </c>
+      <c r="M35" t="n">
         <v>3.9</v>
       </c>
-      <c r="H35" t="n">
-        <v>390</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2758,12 +2955,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>F100E - BATERIA 100AMP</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mercadoria</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2771,29 +2968,33 @@
           <t>Saída</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="n">
+        <v>10</v>
+      </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J36" t="n">
-        <v>510</v>
+        <v>79</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+        <v>79</v>
+      </c>
+      <c r="L36" t="n">
+        <v>29</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2.9</v>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2802,12 +3003,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TC1014 - TAMPA TANQUE ROSCA INT VW MODERNO</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Mercadoria</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2815,29 +3016,33 @@
           <t>Saída</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>0.99</v>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>10</v>
+      </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J37" t="n">
-        <v>59.4</v>
+        <v>79</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+        <v>79</v>
+      </c>
+      <c r="L37" t="n">
+        <v>39</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.9</v>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2846,12 +3051,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1932231 - EMBREAGEM VISCOSA</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mercadoria</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2859,29 +3064,33 @@
           <t>Saída</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>45</v>
+      </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J38" t="n">
-        <v>5.5</v>
+        <v>310.5</v>
       </c>
       <c r="K38" t="n">
-        <v>550</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+        <v>310.5</v>
+      </c>
+      <c r="L38" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2.9</v>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2890,42 +3099,46 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1932231 - EMBREAGEM VISCOSA</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mercadoria</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>0.99</v>
-      </c>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="H39" t="n">
+        <v>100</v>
+      </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="J39" t="n">
-        <v>544.5</v>
+        <v>290</v>
       </c>
       <c r="K39" t="n">
-        <v>550</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2934,12 +3147,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>F100E - BATERIA 100AMP</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mercadoria</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2947,29 +3160,33 @@
           <t>Saída</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="n">
+        <v>55</v>
+      </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J40" t="n">
-        <v>510</v>
+        <v>434.5</v>
       </c>
       <c r="K40" t="n">
-        <v>510</v>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+        <v>434.5</v>
+      </c>
+      <c r="L40" t="n">
+        <v>214.5</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.9</v>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2978,51 +3195,55 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TC1014 - TAMPA TANQUE ROSCA INT VW MODERNO</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mercadoria</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>0.01</v>
-      </c>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="n">
+        <v>100</v>
+      </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6</v>
+        <v>390</v>
       </c>
       <c r="K41" t="n">
-        <v>60</v>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TC1014 - TAMPA TANQUE ROSCA INT VW MODERNO</t>
+          <t>F100E - BATERIA 100AMP</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3032,57 +3253,41 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" t="n">
-        <v>60</v>
-      </c>
-      <c r="H42" t="n">
-        <v>60</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="n">
         <v>0</v>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>MULTIMARCAS PECAS DIESEL LTDA</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>33260509637385000410550020000482621038100650</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Entrada automática por XML. Código: 1297 | NCM: 87089990 | CFOP: 5405</t>
-        </is>
-      </c>
+      <c r="L42" t="n">
+        <v>510</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1932231 - EMBREAGEM VISCOSA</t>
+          <t>TC1014 - TAMPA TANQUE ROSCA INT VW MODERNO</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3092,102 +3297,622 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>550</v>
-      </c>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>550</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
+        <v>0.99</v>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="n">
         <v>0</v>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>MULTIMARCAS PECAS DIESEL LTDA</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>33260509637385000410550020000482621038100650</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Entrada automática por XML. Código: 8789 | NCM: 84836019 | CFOP: 5405</t>
-        </is>
-      </c>
+      <c r="L43" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
+        <v>7</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1932231 - EMBREAGEM VISCOSA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Mercadoria</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M44" t="n">
+        <v>550</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>6</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1932231 - EMBREAGEM VISCOSA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Mercadoria</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>544.5</v>
+      </c>
+      <c r="M45" t="n">
+        <v>550</v>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>F100E - BATERIA 100AMP</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Mercadoria</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="n">
         <v>1</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>510</v>
+      </c>
+      <c r="M46" t="n">
+        <v>510</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TC1014 - TAMPA TANQUE ROSCA INT VW MODERNO</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Mercadoria</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M47" t="n">
+        <v>60</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TC1014 - TAMPA TANQUE ROSCA INT VW MODERNO</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Mercadoria</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>60</v>
+      </c>
+      <c r="J48" t="n">
+        <v>60</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>MULTIMARCAS PECAS DIESEL LTDA</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>33260509637385000410550020000482621038100650</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Entrada automática por XML. Código: 1297 | NCM: 87089990 | CFOP: 5405</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1932231 - EMBREAGEM VISCOSA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Mercadoria</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>550</v>
+      </c>
+      <c r="J49" t="n">
+        <v>550</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>MULTIMARCAS PECAS DIESEL LTDA</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>33260509637385000410550020000482621038100650</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Entrada automática por XML. Código: 8789 | NCM: 84836019 | CFOP: 5405</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
         <is>
           <t>F100E - BATERIA 100AMP</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Mercadoria</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Entrada</t>
         </is>
       </c>
-      <c r="F44" t="n">
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="n">
         <v>2</v>
       </c>
-      <c r="G44" t="n">
+      <c r="I50" t="n">
         <v>510</v>
       </c>
-      <c r="H44" t="n">
+      <c r="J50" t="n">
         <v>1020</v>
       </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t>MULTIMARCAS PECAS DIESEL LTDA</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>33260509637385000410550020000482621038100650</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>Entrada automática por XML. Código: 14541 | NCM: 85071090 | CFOP: 5405</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>53</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CROISSANT INT DE MINAS COM CEB SC 2,5 KG</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Mercadoria</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>80</v>
+      </c>
+      <c r="J51" t="n">
+        <v>80</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Forno e Sabor - Folhados e Croissants Ltda</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>33260360593701000103550000000021961178700803</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>XML Código 001338 NCM 19059090 CFOP 5405</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>52</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CROISSANT DE PIZZA LIGHT SC C 2,5 KG</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Mercadoria</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>74</v>
+      </c>
+      <c r="J52" t="n">
+        <v>74</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Forno e Sabor - Folhados e Croissants Ltda</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>33260360593701000103550000000021961178700803</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>XML Código 001008 NCM 19059090 CFOP 5405</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CROISSANT DE FRANGO COM REQUEIJAO SC 2,8 KG</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Mercadoria</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="n">
+        <v>3</v>
+      </c>
+      <c r="I53" t="n">
+        <v>74</v>
+      </c>
+      <c r="J53" t="n">
+        <v>222</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Forno e Sabor - Folhados e Croissants Ltda</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>33260360593701000103550000000021961178700803</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>XML Código 001002 NCM 19059090 CFOP 5405</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CROISSANT MISTO SC 2,8 KG</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Mercadoria</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="n">
+        <v>3</v>
+      </c>
+      <c r="I54" t="n">
+        <v>74</v>
+      </c>
+      <c r="J54" t="n">
+        <v>222</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Forno e Sabor - Folhados e Croissants Ltda</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>33260360593701000103550000000021961178700803</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>XML Código 001001 NCM 19059090 CFOP 5405</t>
         </is>
       </c>
     </row>
@@ -3202,61 +3927,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Produto</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Data Entrada</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Qtd Inicial</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Qtd Restante</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Valor Unitário</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Valor Restante</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Fornecedor</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Chave NF-e</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
@@ -3285,13 +4010,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>8.673617379884035e-18</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>550</v>
       </c>
       <c r="H2" t="n">
-        <v>4.77048955893622e-15</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3332,13 +4057,13 @@
         <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G3" t="n">
         <v>2.9</v>
       </c>
       <c r="H3" t="n">
-        <v>145</v>
+        <v>139.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3371,13 +4096,13 @@
         <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
         <v>5.5</v>
       </c>
       <c r="H4" t="n">
-        <v>275</v>
+        <v>247.5</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -3385,159 +4110,199 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>CROISSANT DE FRANGO COM REQUEIJAO SC 2,8 KG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Mercadoria</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>3.9</v>
+        <v>74</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+        <v>222</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Forno e Sabor - Folhados e Croissants Ltda</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>33260360593701000103550000000021961178700803</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>XML Código 001002 NCM 19059090 CFOP 5405</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>CROISSANT DE PIZZA LIGHT SC C 2,5 KG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Mercadoria</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9</v>
+        <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>Forno e Sabor - Folhados e Croissants Ltda</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>33260360593701000103550000000021961178700803</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>XML Código 001008 NCM 19059090 CFOP 5405</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>CROISSANT INT DE MINAS COM CEB SC 2,5 KG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Mercadoria</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9</v>
+        <v>80</v>
       </c>
       <c r="H7" t="n">
-        <v>145</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Forno e Sabor - Folhados e Croissants Ltda</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>33260360593701000103550000000021961178700803</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>XML Código 001338 NCM 19059090 CFOP 5405</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Croissant Frango Requeijão</t>
+          <t>CROISSANT MISTO SC 2,8 KG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Mercadoria</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>45.8</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>74</v>
       </c>
       <c r="H8" t="n">
-        <v>132.82</v>
+        <v>222</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>Forno e Sabor - Folhados e Croissants Ltda</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>33260360593701000103550000000021961178700803</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>XML Código 001001 NCM 19059090 CFOP 5405</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3557,7 +4322,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -3568,11 +4333,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3607,11 +4372,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3628,13 +4393,13 @@
         <v>50</v>
       </c>
       <c r="F11" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G11" t="n">
         <v>2.9</v>
       </c>
       <c r="H11" t="n">
-        <v>145</v>
+        <v>136.3</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -3642,11 +4407,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Croissant Ricota</t>
+          <t>Croissant Frango Requeijão</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3656,20 +4421,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>32.8</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>95.11999999999999</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -3681,11 +4446,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Croissant Ricota</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3695,20 +4460,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>2.9</v>
       </c>
       <c r="H13" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
@@ -3716,81 +4481,73 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>F100E - BATERIA 100AMP</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mercadoria</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>510</v>
+        <v>1.9</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MULTIMARCAS PECAS DIESEL LTDA</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>33260509637385000410550020000482621038100650</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Entrada automática por XML. Código: 14541 | NCM: 85071090 | CFOP: 5405</t>
-        </is>
-      </c>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pastel Carne</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -3798,51 +4555,55 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pastel Carne</t>
+          <t>Croissant Ricota</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>1.9</v>
       </c>
       <c r="H16" t="n">
-        <v>95</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pastel Natural Frango</t>
+          <t>Croissant Ricota</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3854,13 +4615,13 @@
         <v>50</v>
       </c>
       <c r="F17" t="n">
-        <v>46.8</v>
+        <v>50</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="H17" t="n">
-        <v>88.91999999999999</v>
+        <v>145</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -3868,46 +4629,58 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pastel Queijo</t>
+          <t>F100E - BATERIA 100AMP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Mercadoria</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7</v>
+        <v>510</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MULTIMARCAS PECAS DIESEL LTDA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>33260509637385000410550020000482621038100650</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Entrada automática por XML. Código: 14541 | NCM: 85071090 | CFOP: 5405</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pastel Queijo</t>
+          <t>Pastel Carne</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3917,20 +4690,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="H19" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
@@ -3938,46 +4711,186 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pastel Carne</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Pastel</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" t="n">
+        <v>50</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H20" t="n">
+        <v>95</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pastel Natural Frango</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Pastel</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>50</v>
+      </c>
+      <c r="F21" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H21" t="n">
+        <v>88.91999999999999</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pastel Queijo</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Pastel</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>150</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pastel Queijo</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Pastel</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>50</v>
+      </c>
+      <c r="F23" t="n">
+        <v>50</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H23" t="n">
+        <v>95</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
         <v>3</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>TC1014 - TAMPA TANQUE ROSCA INT VW MODERNO</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Mercadoria</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E24" t="n">
         <v>1</v>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
         <v>60</v>
       </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>MULTIMARCAS PECAS DIESEL LTDA</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>33260509637385000410550020000482621038100650</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Entrada automática por XML. Código: 1297 | NCM: 87089990 | CFOP: 5405</t>
         </is>
@@ -3994,71 +4907,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Produto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Tipo Saída</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Qtd Saída</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Receita</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>CMV Venda</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>CMV Perdas/Outras Saídas</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>CMV Total</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>CMV Venda %</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>CMV Total %</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Lucro Bruto</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Margem Bruta %</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -4130,31 +5043,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E3" t="n">
-        <v>2125</v>
+        <v>2163.7</v>
       </c>
       <c r="F3" t="n">
-        <v>675</v>
+        <v>683.7</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>675</v>
+        <v>683.7</v>
       </c>
       <c r="I3" t="n">
-        <v>31.76470588235294</v>
+        <v>31.59865045986043</v>
       </c>
       <c r="J3" t="n">
-        <v>31.76470588235294</v>
+        <v>31.59865045986043</v>
       </c>
       <c r="K3" t="n">
-        <v>1450</v>
+        <v>1480</v>
       </c>
       <c r="L3" t="n">
-        <v>68.23529411764706</v>
+        <v>68.40134954013956</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -4228,35 +5141,35 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>33.8</v>
       </c>
       <c r="F5" t="n">
-        <v>550</v>
+        <v>555.8</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>550</v>
+        <v>555.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1644.378698224852</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1644.378698224852</v>
       </c>
       <c r="K5" t="n">
-        <v>-550</v>
+        <v>-522</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1544.378698224852</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>✅ OK</t>
+          <t>⚠️ Acima da meta</t>
         </is>
       </c>
     </row>
@@ -4473,31 +5386,31 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.2</v>
+        <v>17.2</v>
       </c>
       <c r="E10" t="n">
-        <v>39.78</v>
+        <v>207.48</v>
       </c>
       <c r="F10" t="n">
-        <v>12.18</v>
+        <v>49.88</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>12.18</v>
+        <v>49.88</v>
       </c>
       <c r="I10" t="n">
-        <v>30.6184012066365</v>
+        <v>24.04087140929246</v>
       </c>
       <c r="J10" t="n">
-        <v>30.6184012066365</v>
+        <v>24.04087140929246</v>
       </c>
       <c r="K10" t="n">
-        <v>27.6</v>
+        <v>157.6</v>
       </c>
       <c r="L10" t="n">
-        <v>69.38159879336349</v>
+        <v>75.95912859070755</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -4508,49 +5421,224 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Açaí</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Açaí</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>32.54437869822485</v>
+      </c>
+      <c r="J11" t="n">
+        <v>32.54437869822485</v>
+      </c>
+      <c r="K11" t="n">
+        <v>57</v>
+      </c>
+      <c r="L11" t="n">
+        <v>67.45562130177515</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Pastel Natural Frango</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Pastel</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Venda</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D12" t="n">
         <v>3.2</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E12" t="n">
         <v>26.88</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F12" t="n">
         <v>6.08</v>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
         <v>6.08</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I12" t="n">
         <v>22.61904761904762</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>22.61904761904762</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K12" t="n">
         <v>20.8</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L12" t="n">
         <v>77.38095238095239</v>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Observação</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Energia</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Funcionários</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Aluguel</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Salários e ordenados</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Aluguel</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Aluguel</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>05/2026</t>
         </is>
       </c>
     </row>

--- a/relatorio_estoque_peps_cmv.xlsx
+++ b/relatorio_estoque_peps_cmv.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -773,13 +773,13 @@
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>136.3</v>
+        <v>49.3</v>
       </c>
       <c r="H8" t="n">
-        <v>2.899999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P54"/>
+  <dimension ref="A1:P55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1218,16 +1218,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Croissant Frango Requeijão</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1247,34 +1247,30 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I2" t="n">
         <v>12.9</v>
       </c>
       <c r="J2" t="n">
-        <v>77.40000000000001</v>
+        <v>387</v>
       </c>
       <c r="K2" t="n">
-        <v>77.40000000000001</v>
+        <v>387</v>
       </c>
       <c r="L2" t="n">
-        <v>17.4</v>
+        <v>87</v>
       </c>
       <c r="M2" t="n">
         <v>2.9</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Saída automática por foto de cupom. Detectado: ,e6 CROLSSANT INT. FRANGO REQUEIJAO</t>
-        </is>
-      </c>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1330,7 +1326,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1339,12 +1335,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Açaí</t>
+          <t>Croissant Frango Requeijão</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Açaí</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1359,30 +1355,34 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>16.9</v>
+        <v>12.9</v>
       </c>
       <c r="J4" t="n">
-        <v>84.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>84.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>27.5</v>
+        <v>17.4</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Saída automática por foto de cupom. Detectado: ,e6 CROLSSANT INT. FRANGO REQUEIJAO</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1932231 - EMBREAGEM VISCOSA</t>
+          <t>Açaí</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mercadoria</t>
+          <t>Açaí</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1411,22 +1411,22 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
         <v>16.9</v>
       </c>
       <c r="J5" t="n">
-        <v>33.8</v>
+        <v>84.5</v>
       </c>
       <c r="K5" t="n">
-        <v>33.8</v>
+        <v>84.5</v>
       </c>
       <c r="L5" t="n">
-        <v>5.800000000000004</v>
+        <v>27.5</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>1932231 - EMBREAGEM VISCOSA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Mercadoria</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1463,22 +1463,22 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>12.9</v>
+        <v>16.9</v>
       </c>
       <c r="J6" t="n">
-        <v>38.7</v>
+        <v>33.8</v>
       </c>
       <c r="K6" t="n">
-        <v>38.7</v>
+        <v>33.8</v>
       </c>
       <c r="L6" t="n">
-        <v>8.699999999999999</v>
+        <v>5.800000000000004</v>
       </c>
       <c r="M6" t="n">
-        <v>2.899999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croissant Frango Requeijão</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1515,34 +1515,30 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
         <v>12.9</v>
       </c>
       <c r="J7" t="n">
-        <v>12.9</v>
+        <v>38.7</v>
       </c>
       <c r="K7" t="n">
-        <v>12.9</v>
+        <v>38.7</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>2.899999999999999</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Saída automática por foto de cupom. Detectado: ,e6 CROLSSANT INT. FRANGO REQUEIJAO</t>
-        </is>
-      </c>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1551,12 +1547,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pastel Natural Frango</t>
+          <t>Croissant Frango Requeijão</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1571,34 +1567,34 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>12.9</v>
       </c>
       <c r="J8" t="n">
-        <v>20.64</v>
+        <v>12.9</v>
       </c>
       <c r="K8" t="n">
-        <v>20.64</v>
+        <v>12.9</v>
       </c>
       <c r="L8" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="M8" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Saída automática por foto de cupom. Detectado: sa PROMOCAO GUARANA NATURAL</t>
+          <t>Saída automática por foto de cupom. Detectado: ,e6 CROLSSANT INT. FRANGO REQUEIJAO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1607,12 +1603,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croissant Frango Requeijão</t>
+          <t>Pastel Natural Frango</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1639,22 +1635,22 @@
         <v>20.64</v>
       </c>
       <c r="L9" t="n">
-        <v>4.64</v>
+        <v>3.04</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Saída automática por foto de cupom. Detectado: 97 PROMO CROIS FRANGO REQUEIJAO</t>
+          <t>Saída automática por foto de cupom. Detectado: sa PROMOCAO GUARANA NATURAL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1663,12 +1659,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pastel Natural Frango</t>
+          <t>Croissant Frango Requeijão</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1686,31 +1682,31 @@
         <v>1.6</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9</v>
+        <v>12.9</v>
       </c>
       <c r="J10" t="n">
-        <v>6.24</v>
+        <v>20.64</v>
       </c>
       <c r="K10" t="n">
-        <v>6.24</v>
+        <v>20.64</v>
       </c>
       <c r="L10" t="n">
-        <v>3.04</v>
+        <v>4.64</v>
       </c>
       <c r="M10" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Saída automática por foto de cupom. Detectado: sa PROMOCAO GUARANA NATURAL</t>
+          <t>Saída automática por foto de cupom. Detectado: 97 PROMO CROIS FRANGO REQUEIJAO</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1719,12 +1715,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croissant Frango Requeijão</t>
+          <t>Pastel Natural Frango</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1751,22 +1747,22 @@
         <v>6.24</v>
       </c>
       <c r="L11" t="n">
-        <v>4.64</v>
+        <v>3.04</v>
       </c>
       <c r="M11" t="n">
-        <v>2.899999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Saída automática por foto de cupom. Detectado: 97 PROMO CROIS FRANGO REQUEIJAO</t>
+          <t>Saída automática por foto de cupom. Detectado: sa PROMOCAO GUARANA NATURAL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1775,46 +1771,54 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Açaí</t>
+          <t>Croissant Frango Requeijão</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Açaí</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>50</v>
+        <v>1.6</v>
       </c>
       <c r="I12" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="J12" t="n">
-        <v>275</v>
+        <v>6.24</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.899999999999999</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Saída automática por foto de cupom. Detectado: 97 PROMO CROIS FRANGO REQUEIJAO</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1823,12 +1827,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pastel Natural Frango</t>
+          <t>Açaí</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Açaí</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1842,10 +1846,10 @@
         <v>50</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>5.5</v>
       </c>
       <c r="J13" t="n">
-        <v>95</v>
+        <v>275</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1862,7 +1866,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1871,7 +1875,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pastel Queijo</t>
+          <t>Pastel Natural Frango</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1910,7 +1914,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1919,7 +1923,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pastel Carne</t>
+          <t>Pastel Queijo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1958,7 +1962,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1967,12 +1971,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croissant Ricota</t>
+          <t>Pastel Carne</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1986,10 +1990,10 @@
         <v>50</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J16" t="n">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2006,7 +2010,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2015,7 +2019,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>Croissant Ricota</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2054,7 +2058,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2063,7 +2067,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2102,7 +2106,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2111,7 +2115,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croissant Frango Requeijão</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2121,44 +2125,36 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Venda</t>
-        </is>
-      </c>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="I19" t="n">
-        <v>12.9</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
-        <v>12.9</v>
+        <v>145</v>
       </c>
       <c r="K19" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Saída automática por foto de cupom. Detectado: ,e6 CROLSSANT INT. FRANGO REQUEIJAO</t>
-        </is>
-      </c>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2177,40 +2173,44 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="K20" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="L20" t="n">
         <v>2.9</v>
       </c>
-      <c r="J20" t="n">
-        <v>145</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
+        <v>2.9</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Saída automática por foto de cupom. Detectado: ,e6 CROLSSANT INT. FRANGO REQUEIJAO</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1932231 - EMBREAGEM VISCOSA</t>
+          <t>Croissant Frango Requeijão</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mercadoria</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2262,55 +2262,59 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pastel Queijo</t>
+          <t>1932231 - EMBREAGEM VISCOSA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Mercadoria</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="I22" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="J22" t="n">
-        <v>1185</v>
+        <v>145</v>
       </c>
       <c r="K22" t="n">
-        <v>1185</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2319,7 +2323,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pastel Carne</t>
+          <t>Pastel Queijo</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2358,7 +2362,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2377,7 +2381,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2386,16 +2390,16 @@
         <v>150</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>7.9</v>
       </c>
       <c r="J24" t="n">
+        <v>1185</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1185</v>
+      </c>
+      <c r="L24" t="n">
         <v>255</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2406,7 +2410,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2415,7 +2419,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pastel Queijo</t>
+          <t>Pastel Carne</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2454,7 +2458,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2463,35 +2467,35 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croissant Ricota</t>
+          <t>Pastel Queijo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="I26" t="n">
-        <v>8.9</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
-        <v>445</v>
+        <v>255</v>
       </c>
       <c r="K26" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2502,7 +2506,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2511,7 +2515,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>Croissant Ricota</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2527,19 +2531,19 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="I27" t="n">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J27" t="n">
-        <v>1380</v>
+        <v>445</v>
       </c>
       <c r="K27" t="n">
-        <v>1380</v>
+        <v>445</v>
       </c>
       <c r="L27" t="n">
-        <v>285</v>
+        <v>95</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -2550,7 +2554,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2559,7 +2563,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2578,13 +2582,13 @@
         <v>150</v>
       </c>
       <c r="I28" t="n">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>1335</v>
+        <v>1380</v>
       </c>
       <c r="K28" t="n">
-        <v>1335</v>
+        <v>1380</v>
       </c>
       <c r="L28" t="n">
         <v>285</v>
@@ -2598,7 +2602,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2607,7 +2611,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2617,7 +2621,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -2626,31 +2630,27 @@
         <v>150</v>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>8.9</v>
       </c>
       <c r="J29" t="n">
+        <v>1335</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1335</v>
+      </c>
+      <c r="L29" t="n">
         <v>285</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2702,7 +2702,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croissant Ricota</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2721,36 +2721,40 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="I31" t="n">
-        <v>8.9</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
-        <v>890</v>
+        <v>285</v>
       </c>
       <c r="K31" t="n">
-        <v>890</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N31" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2769,40 +2773,36 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I32" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J32" t="n">
+        <v>890</v>
+      </c>
+      <c r="K32" t="n">
+        <v>890</v>
+      </c>
+      <c r="L32" t="n">
+        <v>190</v>
+      </c>
+      <c r="M32" t="n">
         <v>1.9</v>
       </c>
-      <c r="J32" t="n">
-        <v>285</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>Croissant Ricota</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2821,36 +2821,40 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="I33" t="n">
-        <v>7.9</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
-        <v>197.5</v>
+        <v>285</v>
       </c>
       <c r="K33" t="n">
-        <v>197.5</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>97.5</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2859,7 +2863,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2875,19 +2879,19 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="I34" t="n">
         <v>7.9</v>
       </c>
       <c r="J34" t="n">
-        <v>355.5</v>
+        <v>197.5</v>
       </c>
       <c r="K34" t="n">
-        <v>355.5</v>
+        <v>197.5</v>
       </c>
       <c r="L34" t="n">
-        <v>130.5</v>
+        <v>97.5</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -2898,7 +2902,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2907,7 +2911,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2923,22 +2927,22 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="I35" t="n">
         <v>7.9</v>
       </c>
       <c r="J35" t="n">
-        <v>79</v>
+        <v>355.5</v>
       </c>
       <c r="K35" t="n">
-        <v>79</v>
+        <v>355.5</v>
       </c>
       <c r="L35" t="n">
-        <v>39</v>
+        <v>130.5</v>
       </c>
       <c r="M35" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -2946,7 +2950,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2955,7 +2959,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2983,10 +2987,10 @@
         <v>79</v>
       </c>
       <c r="L36" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="M36" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -2994,7 +2998,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3003,7 +3007,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3031,10 +3035,10 @@
         <v>79</v>
       </c>
       <c r="L37" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="M37" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -3042,7 +3046,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3051,7 +3055,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3067,22 +3071,22 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="I38" t="n">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="J38" t="n">
-        <v>310.5</v>
+        <v>79</v>
       </c>
       <c r="K38" t="n">
-        <v>310.5</v>
+        <v>79</v>
       </c>
       <c r="L38" t="n">
-        <v>130.5</v>
+        <v>39</v>
       </c>
       <c r="M38" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3090,7 +3094,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3109,28 +3113,28 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="I39" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J39" t="n">
+        <v>310.5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>310.5</v>
+      </c>
+      <c r="L39" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="M39" t="n">
         <v>2.9</v>
-      </c>
-      <c r="J39" t="n">
-        <v>290</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
@@ -3138,7 +3142,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -3147,7 +3151,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3157,28 +3161,28 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="I40" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="J40" t="n">
-        <v>434.5</v>
+        <v>290</v>
       </c>
       <c r="K40" t="n">
-        <v>434.5</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>214.5</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -3186,7 +3190,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3205,28 +3209,28 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="I41" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J41" t="n">
+        <v>434.5</v>
+      </c>
+      <c r="K41" t="n">
+        <v>434.5</v>
+      </c>
+      <c r="L41" t="n">
+        <v>214.5</v>
+      </c>
+      <c r="M41" t="n">
         <v>3.9</v>
-      </c>
-      <c r="J41" t="n">
-        <v>390</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -3234,7 +3238,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3243,31 +3247,35 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>F100E - BATERIA 100AMP</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mercadoria</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J42" t="n">
+        <v>390</v>
+      </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -3278,7 +3286,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -3287,7 +3295,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TC1014 - TAMPA TANQUE ROSCA INT VW MODERNO</t>
+          <t>F100E - BATERIA 100AMP</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3303,7 +3311,7 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
@@ -3311,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>59.4</v>
+        <v>510</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3322,7 +3330,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -3331,7 +3339,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1932231 - EMBREAGEM VISCOSA</t>
+          <t>TC1014 - TAMPA TANQUE ROSCA INT VW MODERNO</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3347,7 +3355,7 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>0.01</v>
+        <v>0.99</v>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
@@ -3355,10 +3363,10 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>5.5</v>
+        <v>59.4</v>
       </c>
       <c r="M44" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
@@ -3366,7 +3374,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -3391,7 +3399,7 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>0.99</v>
+        <v>0.01</v>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
@@ -3399,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>544.5</v>
+        <v>5.5</v>
       </c>
       <c r="M45" t="n">
         <v>550</v>
@@ -3410,7 +3418,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -3419,7 +3427,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>F100E - BATERIA 100AMP</t>
+          <t>1932231 - EMBREAGEM VISCOSA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3435,7 +3443,7 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
@@ -3443,10 +3451,10 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>510</v>
+        <v>544.5</v>
       </c>
       <c r="M46" t="n">
-        <v>510</v>
+        <v>550</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
@@ -3454,7 +3462,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -3463,7 +3471,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TC1014 - TAMPA TANQUE ROSCA INT VW MODERNO</t>
+          <t>F100E - BATERIA 100AMP</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3479,7 +3487,7 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
@@ -3487,10 +3495,10 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0.6</v>
+        <v>510</v>
       </c>
       <c r="M47" t="n">
-        <v>60</v>
+        <v>510</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
@@ -3498,11 +3506,11 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3517,48 +3525,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>1</v>
-      </c>
-      <c r="I48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M48" t="n">
         <v>60</v>
       </c>
-      <c r="J48" t="n">
-        <v>60</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>MULTIMARCAS PECAS DIESEL LTDA</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>33260509637385000410550020000482621038100650</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Entrada automática por XML. Código: 1297 | NCM: 87089990 | CFOP: 5405</t>
-        </is>
-      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -3567,7 +3559,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1932231 - EMBREAGEM VISCOSA</t>
+          <t>TC1014 - TAMPA TANQUE ROSCA INT VW MODERNO</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3586,10 +3578,10 @@
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>550</v>
+        <v>60</v>
       </c>
       <c r="J49" t="n">
-        <v>550</v>
+        <v>60</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -3612,13 +3604,13 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Entrada automática por XML. Código: 8789 | NCM: 84836019 | CFOP: 5405</t>
+          <t>Entrada automática por XML. Código: 1297 | NCM: 87089990 | CFOP: 5405</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -3627,7 +3619,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>F100E - BATERIA 100AMP</t>
+          <t>1932231 - EMBREAGEM VISCOSA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3643,13 +3635,13 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>510</v>
+        <v>550</v>
       </c>
       <c r="J50" t="n">
-        <v>1020</v>
+        <v>550</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -3672,22 +3664,22 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Entrada automática por XML. Código: 14541 | NCM: 85071090 | CFOP: 5405</t>
+          <t>Entrada automática por XML. Código: 8789 | NCM: 84836019 | CFOP: 5405</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CROISSANT INT DE MINAS COM CEB SC 2,5 KG</t>
+          <t>F100E - BATERIA 100AMP</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3703,13 +3695,13 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51" t="n">
-        <v>80</v>
+        <v>510</v>
       </c>
       <c r="J51" t="n">
-        <v>80</v>
+        <v>1020</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -3722,23 +3714,23 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Forno e Sabor - Folhados e Croissants Ltda</t>
+          <t>MULTIMARCAS PECAS DIESEL LTDA</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>33260360593701000103550000000021961178700803</t>
+          <t>33260509637385000410550020000482621038100650</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>XML Código 001338 NCM 19059090 CFOP 5405</t>
+          <t>Entrada automática por XML. Código: 14541 | NCM: 85071090 | CFOP: 5405</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -3747,7 +3739,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CROISSANT DE PIZZA LIGHT SC C 2,5 KG</t>
+          <t>CROISSANT INT DE MINAS COM CEB SC 2,5 KG</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3766,10 +3758,10 @@
         <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="J52" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -3792,13 +3784,13 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>XML Código 001008 NCM 19059090 CFOP 5405</t>
+          <t>XML Código 001338 NCM 19059090 CFOP 5405</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3807,7 +3799,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CROISSANT DE FRANGO COM REQUEIJAO SC 2,8 KG</t>
+          <t>CROISSANT DE PIZZA LIGHT SC C 2,5 KG</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3823,13 +3815,13 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
         <v>74</v>
       </c>
       <c r="J53" t="n">
-        <v>222</v>
+        <v>74</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -3852,13 +3844,13 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>XML Código 001002 NCM 19059090 CFOP 5405</t>
+          <t>XML Código 001008 NCM 19059090 CFOP 5405</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3867,7 +3859,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CROISSANT MISTO SC 2,8 KG</t>
+          <t>CROISSANT DE FRANGO COM REQUEIJAO SC 2,8 KG</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3911,6 +3903,66 @@
         </is>
       </c>
       <c r="P54" t="inlineStr">
+        <is>
+          <t>XML Código 001002 NCM 19059090 CFOP 5405</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CROISSANT MISTO SC 2,8 KG</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Mercadoria</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="n">
+        <v>3</v>
+      </c>
+      <c r="I55" t="n">
+        <v>74</v>
+      </c>
+      <c r="J55" t="n">
+        <v>222</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Forno e Sabor - Folhados e Croissants Ltda</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>33260360593701000103550000000021961178700803</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
         <is>
           <t>XML Código 001001 NCM 19059090 CFOP 5405</t>
         </is>
@@ -4393,13 +4445,13 @@
         <v>50</v>
       </c>
       <c r="F11" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="G11" t="n">
         <v>2.9</v>
       </c>
       <c r="H11" t="n">
-        <v>136.3</v>
+        <v>49.3</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -5043,31 +5095,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="E3" t="n">
-        <v>2163.7</v>
+        <v>2550.7</v>
       </c>
       <c r="F3" t="n">
-        <v>683.7</v>
+        <v>770.7</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>683.7</v>
+        <v>770.7</v>
       </c>
       <c r="I3" t="n">
-        <v>31.59865045986043</v>
+        <v>30.21523503352022</v>
       </c>
       <c r="J3" t="n">
-        <v>31.59865045986043</v>
+        <v>30.21523503352022</v>
       </c>
       <c r="K3" t="n">
-        <v>1480</v>
+        <v>1780</v>
       </c>
       <c r="L3" t="n">
-        <v>68.40134954013956</v>
+        <v>69.78476496647978</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>

--- a/relatorio_estoque_peps_cmv.xlsx
+++ b/relatorio_estoque_peps_cmv.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>247.5</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
         <v>5.5</v>
@@ -773,10 +773,10 @@
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G8" t="n">
-        <v>49.3</v>
+        <v>40.6</v>
       </c>
       <c r="H8" t="n">
         <v>2.9</v>
@@ -810,17 +810,17 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>32.8</v>
+        <v>2.799999999999997</v>
       </c>
       <c r="G9" t="n">
-        <v>95.11999999999999</v>
+        <v>8.119999999999992</v>
       </c>
       <c r="H9" t="n">
         <v>2.9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>⚠️ Baixo</t>
         </is>
       </c>
     </row>
@@ -847,10 +847,10 @@
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>145</v>
+        <v>87</v>
       </c>
       <c r="H10" t="n">
         <v>2.9</v>
@@ -884,10 +884,10 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="H11" t="n">
         <v>2.9</v>
@@ -1131,7 +1131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P55"/>
+  <dimension ref="A1:P60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1218,7 +1218,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>Açaí</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Açaí</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1247,22 +1247,22 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I2" t="n">
-        <v>12.9</v>
+        <v>20.9</v>
       </c>
       <c r="J2" t="n">
-        <v>387</v>
+        <v>522.5</v>
       </c>
       <c r="K2" t="n">
-        <v>387</v>
+        <v>522.5</v>
       </c>
       <c r="L2" t="n">
-        <v>87</v>
+        <v>137.5</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -1270,16 +1270,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Croissant Frango Requeijão</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1294,48 +1294,48 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Venda</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Perda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Vencimento</t>
+        </is>
+      </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>77.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>77.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>17.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M3" t="n">
         <v>2.9</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Saída automática por foto de cupom. Detectado: ,e6 CROLSSANT INT. FRANGO REQUEIJAO</t>
-        </is>
-      </c>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Croissant Frango Requeijão</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1355,48 +1355,44 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I4" t="n">
         <v>12.9</v>
       </c>
       <c r="J4" t="n">
-        <v>77.40000000000001</v>
+        <v>258</v>
       </c>
       <c r="K4" t="n">
-        <v>77.40000000000001</v>
+        <v>258</v>
       </c>
       <c r="L4" t="n">
-        <v>17.4</v>
+        <v>58</v>
       </c>
       <c r="M4" t="n">
         <v>2.9</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Saída automática por foto de cupom. Detectado: ,e6 CROLSSANT INT. FRANGO REQUEIJAO</t>
-        </is>
-      </c>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Açaí</t>
+          <t>Croissant Ricota</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Açaí</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1411,22 +1407,22 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="I5" t="n">
-        <v>16.9</v>
+        <v>12.9</v>
       </c>
       <c r="J5" t="n">
-        <v>84.5</v>
+        <v>387</v>
       </c>
       <c r="K5" t="n">
-        <v>84.5</v>
+        <v>387</v>
       </c>
       <c r="L5" t="n">
-        <v>27.5</v>
+        <v>87</v>
       </c>
       <c r="M5" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -1434,21 +1430,21 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1932231 - EMBREAGEM VISCOSA</t>
+          <t>Croissant Frango Requeijão</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mercadoria</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1463,19 +1459,19 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="I6" t="n">
-        <v>16.9</v>
+        <v>12.9</v>
       </c>
       <c r="J6" t="n">
-        <v>33.8</v>
+        <v>387</v>
       </c>
       <c r="K6" t="n">
-        <v>33.8</v>
+        <v>387</v>
       </c>
       <c r="L6" t="n">
-        <v>5.800000000000004</v>
+        <v>87</v>
       </c>
       <c r="M6" t="n">
         <v>2.9</v>
@@ -1486,11 +1482,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1515,22 +1511,22 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="I7" t="n">
         <v>12.9</v>
       </c>
       <c r="J7" t="n">
-        <v>38.7</v>
+        <v>387</v>
       </c>
       <c r="K7" t="n">
-        <v>38.7</v>
+        <v>387</v>
       </c>
       <c r="L7" t="n">
-        <v>8.699999999999999</v>
+        <v>87</v>
       </c>
       <c r="M7" t="n">
-        <v>2.899999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -1538,7 +1534,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1567,19 +1563,19 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
         <v>12.9</v>
       </c>
       <c r="J8" t="n">
-        <v>12.9</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>12.9</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9</v>
+        <v>17.4</v>
       </c>
       <c r="M8" t="n">
         <v>2.9</v>
@@ -1594,7 +1590,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1603,12 +1599,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pastel Natural Frango</t>
+          <t>Croissant Frango Requeijão</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1623,34 +1619,34 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
         <v>12.9</v>
       </c>
       <c r="J9" t="n">
-        <v>20.64</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>20.64</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>3.04</v>
+        <v>17.4</v>
       </c>
       <c r="M9" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Saída automática por foto de cupom. Detectado: sa PROMOCAO GUARANA NATURAL</t>
+          <t>Saída automática por foto de cupom. Detectado: ,e6 CROLSSANT INT. FRANGO REQUEIJAO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1659,12 +1655,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croissant Frango Requeijão</t>
+          <t>Açaí</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Açaí</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1679,34 +1675,30 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>12.9</v>
+        <v>16.9</v>
       </c>
       <c r="J10" t="n">
-        <v>20.64</v>
+        <v>84.5</v>
       </c>
       <c r="K10" t="n">
-        <v>20.64</v>
+        <v>84.5</v>
       </c>
       <c r="L10" t="n">
-        <v>4.64</v>
+        <v>27.5</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Saída automática por foto de cupom. Detectado: 97 PROMO CROIS FRANGO REQUEIJAO</t>
-        </is>
-      </c>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1715,12 +1707,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pastel Natural Frango</t>
+          <t>1932231 - EMBREAGEM VISCOSA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Mercadoria</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1735,34 +1727,30 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>3.9</v>
+        <v>16.9</v>
       </c>
       <c r="J11" t="n">
-        <v>6.24</v>
+        <v>33.8</v>
       </c>
       <c r="K11" t="n">
-        <v>6.24</v>
+        <v>33.8</v>
       </c>
       <c r="L11" t="n">
-        <v>3.04</v>
+        <v>5.800000000000004</v>
       </c>
       <c r="M11" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Saída automática por foto de cupom. Detectado: sa PROMOCAO GUARANA NATURAL</t>
-        </is>
-      </c>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1771,7 +1759,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croissant Frango Requeijão</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1791,34 +1779,30 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>3.9</v>
+        <v>12.9</v>
       </c>
       <c r="J12" t="n">
-        <v>6.24</v>
+        <v>38.7</v>
       </c>
       <c r="K12" t="n">
-        <v>6.24</v>
+        <v>38.7</v>
       </c>
       <c r="L12" t="n">
-        <v>4.64</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M12" t="n">
         <v>2.899999999999999</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Saída automática por foto de cupom. Detectado: 97 PROMO CROIS FRANGO REQUEIJAO</t>
-        </is>
-      </c>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1827,46 +1811,54 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Açaí</t>
+          <t>Croissant Frango Requeijão</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Açaí</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>5.5</v>
+        <v>12.9</v>
       </c>
       <c r="J13" t="n">
-        <v>275</v>
+        <v>12.9</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Saída automática por foto de cupom. Detectado: ,e6 CROLSSANT INT. FRANGO REQUEIJAO</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1885,36 +1877,44 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>50</v>
+        <v>1.6</v>
       </c>
       <c r="I14" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="M14" t="n">
         <v>1.9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>95</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Saída automática por foto de cupom. Detectado: sa PROMOCAO GUARANA NATURAL</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1923,46 +1923,54 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pastel Queijo</t>
+          <t>Croissant Frango Requeijão</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>50</v>
+        <v>1.6</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>12.9</v>
       </c>
       <c r="J15" t="n">
-        <v>95</v>
+        <v>20.64</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>20.64</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Saída automática por foto de cupom. Detectado: 97 PROMO CROIS FRANGO REQUEIJAO</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1971,7 +1979,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pastel Carne</t>
+          <t>Pastel Natural Frango</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1981,36 +1989,44 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>50</v>
+        <v>1.6</v>
       </c>
       <c r="I16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="M16" t="n">
         <v>1.9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>95</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Saída automática por foto de cupom. Detectado: sa PROMOCAO GUARANA NATURAL</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2019,7 +2035,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croissant Ricota</t>
+          <t>Croissant Frango Requeijão</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2029,36 +2045,44 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>50</v>
+        <v>1.6</v>
       </c>
       <c r="I17" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="J17" t="n">
-        <v>145</v>
+        <v>6.24</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.899999999999999</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Saída automática por foto de cupom. Detectado: 97 PROMO CROIS FRANGO REQUEIJAO</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2067,12 +2091,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>Açaí</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Açaí</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2086,10 +2110,10 @@
         <v>50</v>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="J18" t="n">
-        <v>145</v>
+        <v>275</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2106,7 +2130,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2115,12 +2139,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>Pastel Natural Frango</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2134,10 +2158,10 @@
         <v>50</v>
       </c>
       <c r="I19" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2154,7 +2178,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2163,54 +2187,46 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croissant Frango Requeijão</t>
+          <t>Pastel Queijo</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Venda</t>
-        </is>
-      </c>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="I20" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
-        <v>12.9</v>
+        <v>95</v>
       </c>
       <c r="K20" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Saída automática por foto de cupom. Detectado: ,e6 CROLSSANT INT. FRANGO REQUEIJAO</t>
-        </is>
-      </c>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2219,12 +2235,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croissant Frango Requeijão</t>
+          <t>Pastel Carne</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2238,10 +2254,10 @@
         <v>50</v>
       </c>
       <c r="I21" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2252,17 +2268,13 @@
       <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2271,12 +2283,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1932231 - EMBREAGEM VISCOSA</t>
+          <t>Croissant Ricota</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mercadoria</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2304,54 +2316,50 @@
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pastel Queijo</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="I23" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
-        <v>1185</v>
+        <v>145</v>
       </c>
       <c r="K23" t="n">
-        <v>1185</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2362,44 +2370,44 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pastel Carne</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="I24" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
-        <v>1185</v>
+        <v>145</v>
       </c>
       <c r="K24" t="n">
-        <v>1185</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2410,69 +2418,77 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pastel Carne</t>
+          <t>Croissant Frango Requeijão</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>Saída</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>12.9</v>
       </c>
       <c r="J25" t="n">
-        <v>255</v>
+        <v>12.9</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Saída automática por foto de cupom. Detectado: ,e6 CROLSSANT INT. FRANGO REQUEIJAO</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pastel Queijo</t>
+          <t>Croissant Frango Requeijão</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2483,13 +2499,13 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
-        <v>255</v>
+        <v>145</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2500,32 +2516,36 @@
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croissant Ricota</t>
+          <t>1932231 - EMBREAGEM VISCOSA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Mercadoria</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -2534,27 +2554,31 @@
         <v>50</v>
       </c>
       <c r="I27" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
-        <v>445</v>
+        <v>145</v>
       </c>
       <c r="K27" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2563,12 +2587,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>Pastel Queijo</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2582,16 +2606,16 @@
         <v>150</v>
       </c>
       <c r="I28" t="n">
-        <v>9.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J28" t="n">
-        <v>1380</v>
+        <v>1185</v>
       </c>
       <c r="K28" t="n">
-        <v>1380</v>
+        <v>1185</v>
       </c>
       <c r="L28" t="n">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2602,7 +2626,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2611,12 +2635,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>Pastel Carne</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2630,16 +2654,16 @@
         <v>150</v>
       </c>
       <c r="I29" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="J29" t="n">
-        <v>1335</v>
+        <v>1185</v>
       </c>
       <c r="K29" t="n">
-        <v>1335</v>
+        <v>1185</v>
       </c>
       <c r="L29" t="n">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -2650,7 +2674,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2659,12 +2683,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>Pastel Carne</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2678,10 +2702,10 @@
         <v>150</v>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2692,17 +2716,13 @@
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2711,12 +2731,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>Pastel Queijo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2730,10 +2750,10 @@
         <v>150</v>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -2744,17 +2764,13 @@
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2779,22 +2795,22 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I32" t="n">
         <v>8.9</v>
       </c>
       <c r="J32" t="n">
-        <v>890</v>
+        <v>445</v>
       </c>
       <c r="K32" t="n">
-        <v>890</v>
+        <v>445</v>
       </c>
       <c r="L32" t="n">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="M32" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -2802,7 +2818,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2811,7 +2827,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Croissant Ricota</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2821,7 +2837,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -2830,31 +2846,27 @@
         <v>150</v>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J33" t="n">
+        <v>1380</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1380</v>
+      </c>
+      <c r="L33" t="n">
         <v>285</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2879,19 +2891,19 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="I34" t="n">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
       <c r="J34" t="n">
-        <v>197.5</v>
+        <v>1335</v>
       </c>
       <c r="K34" t="n">
-        <v>197.5</v>
+        <v>1335</v>
       </c>
       <c r="L34" t="n">
-        <v>97.5</v>
+        <v>285</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -2902,7 +2914,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2921,36 +2933,40 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>45</v>
+        <v>150</v>
       </c>
       <c r="I35" t="n">
-        <v>7.9</v>
+        <v>1.9</v>
       </c>
       <c r="J35" t="n">
-        <v>355.5</v>
+        <v>285</v>
       </c>
       <c r="K35" t="n">
-        <v>355.5</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>130.5</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2969,36 +2985,40 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="I36" t="n">
-        <v>7.9</v>
+        <v>1.9</v>
       </c>
       <c r="J36" t="n">
-        <v>79</v>
+        <v>285</v>
       </c>
       <c r="K36" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N36" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3007,7 +3027,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>Croissant Ricota</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3023,22 +3043,22 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
       <c r="J37" t="n">
-        <v>79</v>
+        <v>890</v>
       </c>
       <c r="K37" t="n">
-        <v>79</v>
+        <v>890</v>
       </c>
       <c r="L37" t="n">
-        <v>29</v>
+        <v>190</v>
       </c>
       <c r="M37" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -3046,7 +3066,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3055,7 +3075,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>Croissant Ricota</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3065,36 +3085,40 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="I38" t="n">
-        <v>7.9</v>
+        <v>1.9</v>
       </c>
       <c r="J38" t="n">
-        <v>79</v>
+        <v>285</v>
       </c>
       <c r="K38" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N38" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3103,7 +3127,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croissant Queijo Presunto</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3119,22 +3143,22 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="I39" t="n">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="J39" t="n">
-        <v>310.5</v>
+        <v>197.5</v>
       </c>
       <c r="K39" t="n">
-        <v>310.5</v>
+        <v>197.5</v>
       </c>
       <c r="L39" t="n">
-        <v>130.5</v>
+        <v>97.5</v>
       </c>
       <c r="M39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
@@ -3142,7 +3166,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -3161,25 +3185,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="I40" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="J40" t="n">
-        <v>290</v>
+        <v>355.5</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>355.5</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>130.5</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -3190,7 +3214,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3215,19 +3239,19 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="I41" t="n">
         <v>7.9</v>
       </c>
       <c r="J41" t="n">
-        <v>434.5</v>
+        <v>79</v>
       </c>
       <c r="K41" t="n">
-        <v>434.5</v>
+        <v>79</v>
       </c>
       <c r="L41" t="n">
-        <v>214.5</v>
+        <v>39</v>
       </c>
       <c r="M41" t="n">
         <v>3.9</v>
@@ -3238,7 +3262,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3247,7 +3271,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Croissant Carne</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3257,28 +3281,28 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I42" t="n">
-        <v>3.9</v>
+        <v>7.9</v>
       </c>
       <c r="J42" t="n">
-        <v>390</v>
+        <v>79</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -3286,7 +3310,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -3295,12 +3319,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>F100E - BATERIA 100AMP</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mercadoria</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3311,18 +3335,22 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I43" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J43" t="n">
+        <v>79</v>
+      </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="L43" t="n">
-        <v>510</v>
+        <v>39</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -3330,7 +3358,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -3339,12 +3367,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TC1014 - TAMPA TANQUE ROSCA INT VW MODERNO</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mercadoria</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3355,18 +3383,22 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="I44" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J44" t="n">
+        <v>310.5</v>
+      </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>310.5</v>
       </c>
       <c r="L44" t="n">
-        <v>59.4</v>
+        <v>130.5</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
@@ -3374,7 +3406,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -3383,34 +3415,38 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1932231 - EMBREAGEM VISCOSA</t>
+          <t>Croissant Queijo Presunto</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mercadoria</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J45" t="n">
+        <v>290</v>
+      </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
@@ -3418,7 +3454,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -3427,12 +3463,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1932231 - EMBREAGEM VISCOSA</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Mercadoria</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3443,18 +3479,22 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="I46" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J46" t="n">
+        <v>434.5</v>
+      </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>434.5</v>
       </c>
       <c r="L46" t="n">
-        <v>544.5</v>
+        <v>214.5</v>
       </c>
       <c r="M46" t="n">
-        <v>550</v>
+        <v>3.9</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
@@ -3462,7 +3502,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -3471,34 +3511,38 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>F100E - BATERIA 100AMP</t>
+          <t>Croissant Carne</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mercadoria</t>
+          <t>Croissant</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>1</v>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J47" t="n">
+        <v>390</v>
+      </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
@@ -3506,7 +3550,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -3515,7 +3559,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TC1014 - TAMPA TANQUE ROSCA INT VW MODERNO</t>
+          <t>F100E - BATERIA 100AMP</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3531,7 +3575,7 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
@@ -3539,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0.6</v>
+        <v>510</v>
       </c>
       <c r="M48" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
@@ -3550,11 +3594,11 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3569,52 +3613,36 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>1</v>
-      </c>
-      <c r="I49" t="n">
-        <v>60</v>
-      </c>
-      <c r="J49" t="n">
-        <v>60</v>
-      </c>
+        <v>0.99</v>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>59.4</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>MULTIMARCAS PECAS DIESEL LTDA</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>33260509637385000410550020000482621038100650</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Entrada automática por XML. Código: 1297 | NCM: 87089990 | CFOP: 5405</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3629,57 +3657,41 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M50" t="n">
         <v>550</v>
       </c>
-      <c r="J50" t="n">
-        <v>550</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>MULTIMARCAS PECAS DIESEL LTDA</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>33260509637385000410550020000482621038100650</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Entrada automática por XML. Código: 8789 | NCM: 84836019 | CFOP: 5405</t>
-        </is>
-      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>F100E - BATERIA 100AMP</t>
+          <t>1932231 - EMBREAGEM VISCOSA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3689,57 +3701,41 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>2</v>
-      </c>
-      <c r="I51" t="n">
-        <v>510</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1020</v>
-      </c>
+        <v>0.99</v>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>544.5</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>MULTIMARCAS PECAS DIESEL LTDA</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>33260509637385000410550020000482621038100650</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Entrada automática por XML. Código: 14541 | NCM: 85071090 | CFOP: 5405</t>
-        </is>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CROISSANT INT DE MINAS COM CEB SC 2,5 KG</t>
+          <t>F100E - BATERIA 100AMP</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3749,7 +3745,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -3757,49 +3753,33 @@
       <c r="H52" t="n">
         <v>1</v>
       </c>
-      <c r="I52" t="n">
-        <v>80</v>
-      </c>
-      <c r="J52" t="n">
-        <v>80</v>
-      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Forno e Sabor - Folhados e Croissants Ltda</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>33260360593701000103550000000021961178700803</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>XML Código 001338 NCM 19059090 CFOP 5405</t>
-        </is>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CROISSANT DE PIZZA LIGHT SC C 2,5 KG</t>
+          <t>TC1014 - TAMPA TANQUE ROSCA INT VW MODERNO</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3809,57 +3789,41 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>1</v>
-      </c>
-      <c r="I53" t="n">
-        <v>74</v>
-      </c>
-      <c r="J53" t="n">
-        <v>74</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Forno e Sabor - Folhados e Croissants Ltda</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>33260360593701000103550000000021961178700803</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>XML Código 001008 NCM 19059090 CFOP 5405</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CROISSANT DE FRANGO COM REQUEIJAO SC 2,8 KG</t>
+          <t>TC1014 - TAMPA TANQUE ROSCA INT VW MODERNO</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3875,13 +3839,13 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="J54" t="n">
-        <v>222</v>
+        <v>60</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -3894,32 +3858,32 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Forno e Sabor - Folhados e Croissants Ltda</t>
+          <t>MULTIMARCAS PECAS DIESEL LTDA</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>33260360593701000103550000000021961178700803</t>
+          <t>33260509637385000410550020000482621038100650</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>XML Código 001002 NCM 19059090 CFOP 5405</t>
+          <t>Entrada automática por XML. Código: 1297 | NCM: 87089990 | CFOP: 5405</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CROISSANT MISTO SC 2,8 KG</t>
+          <t>1932231 - EMBREAGEM VISCOSA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3935,34 +3899,334 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>550</v>
+      </c>
+      <c r="J55" t="n">
+        <v>550</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>MULTIMARCAS PECAS DIESEL LTDA</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>33260509637385000410550020000482621038100650</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Entrada automática por XML. Código: 8789 | NCM: 84836019 | CFOP: 5405</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>F100E - BATERIA 100AMP</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Mercadoria</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" t="n">
+        <v>510</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1020</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>MULTIMARCAS PECAS DIESEL LTDA</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>33260509637385000410550020000482621038100650</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Entrada automática por XML. Código: 14541 | NCM: 85071090 | CFOP: 5405</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CROISSANT INT DE MINAS COM CEB SC 2,5 KG</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Mercadoria</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>80</v>
+      </c>
+      <c r="J57" t="n">
+        <v>80</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Forno e Sabor - Folhados e Croissants Ltda</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>33260360593701000103550000000021961178700803</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>XML Código 001338 NCM 19059090 CFOP 5405</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>52</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CROISSANT DE PIZZA LIGHT SC C 2,5 KG</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Mercadoria</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>74</v>
+      </c>
+      <c r="J58" t="n">
+        <v>74</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Forno e Sabor - Folhados e Croissants Ltda</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>33260360593701000103550000000021961178700803</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>XML Código 001008 NCM 19059090 CFOP 5405</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>51</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CROISSANT DE FRANGO COM REQUEIJAO SC 2,8 KG</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Mercadoria</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="n">
         <v>3</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I59" t="n">
         <v>74</v>
       </c>
-      <c r="J55" t="n">
+      <c r="J59" t="n">
         <v>222</v>
       </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="inlineStr">
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>Forno e Sabor - Folhados e Croissants Ltda</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>33260360593701000103550000000021961178700803</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>XML Código 001002 NCM 19059090 CFOP 5405</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>50</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>CROISSANT MISTO SC 2,8 KG</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Mercadoria</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="n">
+        <v>3</v>
+      </c>
+      <c r="I60" t="n">
+        <v>74</v>
+      </c>
+      <c r="J60" t="n">
+        <v>222</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Forno e Sabor - Folhados e Croissants Ltda</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>33260360593701000103550000000021961178700803</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
         <is>
           <t>XML Código 001001 NCM 19059090 CFOP 5405</t>
         </is>
@@ -4148,13 +4412,13 @@
         <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
         <v>5.5</v>
       </c>
       <c r="H4" t="n">
-        <v>247.5</v>
+        <v>110</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -4445,13 +4709,13 @@
         <v>50</v>
       </c>
       <c r="F11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G11" t="n">
         <v>2.9</v>
       </c>
       <c r="H11" t="n">
-        <v>49.3</v>
+        <v>40.6</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -4480,13 +4744,13 @@
         <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>32.8</v>
+        <v>2.799999999999997</v>
       </c>
       <c r="G12" t="n">
         <v>2.9</v>
       </c>
       <c r="H12" t="n">
-        <v>95.11999999999999</v>
+        <v>8.119999999999992</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -4593,13 +4857,13 @@
         <v>50</v>
       </c>
       <c r="F15" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G15" t="n">
         <v>2.9</v>
       </c>
       <c r="H15" t="n">
-        <v>145</v>
+        <v>87</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -4667,13 +4931,13 @@
         <v>50</v>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G17" t="n">
         <v>2.9</v>
       </c>
       <c r="H17" t="n">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -4959,7 +5223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5144,31 +5408,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="E4" t="n">
-        <v>2125</v>
+        <v>2383</v>
       </c>
       <c r="F4" t="n">
-        <v>575</v>
+        <v>633</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>575</v>
+        <v>633</v>
       </c>
       <c r="I4" t="n">
-        <v>27.05882352941176</v>
+        <v>26.56315568610995</v>
       </c>
       <c r="J4" t="n">
-        <v>27.05882352941176</v>
+        <v>26.56315568610995</v>
       </c>
       <c r="K4" t="n">
-        <v>1550</v>
+        <v>1750</v>
       </c>
       <c r="L4" t="n">
-        <v>72.94117647058823</v>
+        <v>73.43684431389006</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -5242,31 +5506,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="E6" t="n">
-        <v>1335</v>
+        <v>1722</v>
       </c>
       <c r="F6" t="n">
-        <v>285</v>
+        <v>372</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>285</v>
+        <v>372</v>
       </c>
       <c r="I6" t="n">
-        <v>21.34831460674157</v>
+        <v>21.60278745644599</v>
       </c>
       <c r="J6" t="n">
-        <v>21.34831460674157</v>
+        <v>21.60278745644599</v>
       </c>
       <c r="K6" t="n">
-        <v>1050</v>
+        <v>1350</v>
       </c>
       <c r="L6" t="n">
-        <v>78.65168539325843</v>
+        <v>78.39721254355401</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -5375,12 +5639,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TC1014 - TAMPA TANQUE ROSCA INT VW MODERNO</t>
+          <t>Açaí</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mercadoria</t>
+          <t>Açaí</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5389,31 +5653,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>607</v>
       </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>27.18286655683691</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>27.18286655683691</v>
       </c>
       <c r="K9" t="n">
-        <v>-60</v>
+        <v>442</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>72.8171334431631</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -5438,31 +5702,31 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.2</v>
+        <v>47.2</v>
       </c>
       <c r="E10" t="n">
-        <v>207.48</v>
+        <v>594.48</v>
       </c>
       <c r="F10" t="n">
-        <v>49.88</v>
+        <v>136.88</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>49.88</v>
+        <v>136.88</v>
       </c>
       <c r="I10" t="n">
-        <v>24.04087140929246</v>
+        <v>23.0251648499529</v>
       </c>
       <c r="J10" t="n">
-        <v>24.04087140929246</v>
+        <v>23.0251648499529</v>
       </c>
       <c r="K10" t="n">
-        <v>157.6</v>
+        <v>457.6</v>
       </c>
       <c r="L10" t="n">
-        <v>75.95912859070755</v>
+        <v>76.9748351500471</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -5473,12 +5737,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Açaí</t>
+          <t>TC1014 - TAMPA TANQUE ROSCA INT VW MODERNO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Açaí</t>
+          <t>Mercadoria</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5487,31 +5751,31 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>84.5</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>27.5</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>27.5</v>
+        <v>60</v>
       </c>
       <c r="I11" t="n">
-        <v>32.54437869822485</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>32.54437869822485</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>57</v>
+        <v>-60</v>
       </c>
       <c r="L11" t="n">
-        <v>67.45562130177515</v>
+        <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -5522,47 +5786,96 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Croissant Carne</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Croissant</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Perda</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>✅ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Pastel Natural Frango</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Pastel</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Venda</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D13" t="n">
         <v>3.2</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E13" t="n">
         <v>26.88</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F13" t="n">
         <v>6.08</v>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
         <v>6.08</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>22.61904761904762</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>22.61904761904762</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>20.8</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>77.38095238095239</v>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>✅ OK</t>
         </is>
@@ -5579,7 +5892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5640,7 +5953,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -5649,7 +5962,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Funcionários</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5658,37 +5971,9 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>21000</v>
+        <v>2000</v>
       </c>
       <c r="F3" t="inlineStr">
-        <is>
-          <t>Salários e ordenados</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Aluguel</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Aluguel</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F4" t="inlineStr">
         <is>
           <t>05/2026</t>
         </is>
